--- a/data/trans_dic/P13A_1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_2023-Provincia-trans_dic.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,78; 100,0</t>
+          <t>80,05; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,24; 100,0</t>
+          <t>86,23; 100,0</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,02; 100,0</t>
+          <t>84,35; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,42; 100,0</t>
+          <t>87,99; 100,0</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,35; 100,0</t>
+          <t>62,54; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,36; 100,0</t>
+          <t>68,46; 100,0</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,71; 100,0</t>
+          <t>80,74; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,81; 100,0</t>
+          <t>87,64; 100,0</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,27; 99,22</t>
+          <t>77,14; 98,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,16; 99,65</t>
+          <t>81,44; 98,7</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>71,12; 100,0</t>
+          <t>68,64; 100,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,92; 100,0</t>
+          <t>63,97; 100,0</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88,46; 97,41</t>
+          <t>88,96; 97,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90,82; 97,98</t>
+          <t>90,62; 97,63</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>40821</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22896; 28345</t>
+          <t>23485; 29340</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35698; 41394</t>
+          <t>36658; 42511</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>22890</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14066; 16544</t>
+          <t>15341; 18187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19154; 21911</t>
+          <t>20637; 23453</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6546</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2973; 4620</t>
+          <t>3067; 4904</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4741; 6644</t>
+          <t>4760; 6952</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18495</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10289; 12749</t>
+          <t>10337; 12802</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16812; 18930</t>
+          <t>16633; 18979</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>48419</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>57333</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30960; 43105</t>
+          <t>40497; 51746</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39834; 50784</t>
+          <t>50016; 60613</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>21420</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17563; 24695</t>
+          <t>15335; 22340</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18744; 25703</t>
+          <t>15022; 23485</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>134306; 147895</t>
+          <t>146218; 159931</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>171861; 185399</t>
+          <t>185120; 199435</t>
         </is>
       </c>
     </row>
